--- a/astro-site/public/dl/guia-restaurante-gastronomico/checklist-equipamiento-cocina.xlsx
+++ b/astro-site/public/dl/guia-restaurante-gastronomico/checklist-equipamiento-cocina.xlsx
@@ -11,6 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet'!$A$4:$H$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Sheet'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +490,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -518,6 +519,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2180,6 +2182,7 @@
       </c>
       <c r="H58" s="6" t="n"/>
     </row>
+    <row r="59"/>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
@@ -2199,6 +2202,15 @@
       <formula1>"Pendiente,En Curso,Completado"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/guia-restaurante-gastronomico/checklist-equipamiento-cocina.xlsx
+++ b/astro-site/public/dl/guia-restaurante-gastronomico/checklist-equipamiento-cocina.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipamiento Cocina" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet'!$A$4:$H$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Sheet'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Equipamiento Cocina'!$A$4:$H$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Equipamiento Cocina'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,10 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +61,25 @@
       <color rgb="00888888"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font/>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +96,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
         <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -127,10 +152,86 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00595959"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F2F2F2"/>
+          <bgColor rgb="00F2F2F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -492,17 +593,146 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Checklist Equipamiento Cocina</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AI Chef Pro · aichef.pro — Restaurante Gastronómico</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Instrucciones de uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1. Rellena las celdas verdes con tus datos; el resto lo calcula el libro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2. Las hojas están protegidas SIN contraseña para que una copia accidental no borre una fórmula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Celdas verdes = campos editables</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Parámetros de este libro (edítalos: el libro recalcula)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Instalación, transporte y puesta en marcha (%)</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>12 % sobre la suma del resto de partidas de este checklist (SPEC §3.4). Es lo que cuesta subir, colocar, conexionar y poner en marcha la maquinaria, y no estaba presupuestado en ninguna línea. NO se aplica sobre las categorías «Extracción e instalaciones» ni «Tecnología»: la primera YA es obra e instalación y la segunda la monta otro proveedor. Cámbialo y el importe se recalcula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Para editar la estructura o una celda que no esté en verde: Revisar → Desproteger hoja (no tiene contraseña).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/guia-restaurante-gastronomico · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Porcentaje" error="Escribe un porcentaje entre 0 y 1 (0,20 = 20 %)." promptTitle="Porcentaje" prompt="Se escribe en tanto por uno: 0,20 = 20 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1.0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -561,6 +791,11 @@
           <t>Notas</t>
         </is>
       </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Incluir en el total</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -576,21 +811,26 @@
           <t>Mesa refrigerada 2 puertas</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>Jefe Partida</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="n">
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="n">
         <v>3500</v>
       </c>
-      <c r="H5" s="6" t="n"/>
+      <c r="H5" s="15" t="n"/>
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -606,21 +846,26 @@
           <t>Cortadora de fiambres profesional</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="n">
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="H6" s="6" t="n"/>
+      <c r="H6" s="15" t="n"/>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -633,24 +878,29 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Abatidor de temperatura 10 GN</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+          <t>Abatidor de temperatura 10 GN</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>Chef</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="n">
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="n">
         <v>5000</v>
       </c>
-      <c r="H7" s="6" t="n"/>
+      <c r="H7" s="15" t="n"/>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -666,21 +916,26 @@
           <t>Envasadora al vacío profesional</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>Chef</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="n">
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="n">
         <v>2500</v>
       </c>
-      <c r="H8" s="6" t="n"/>
+      <c r="H8" s="15" t="n"/>
+      <c r="I8" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -696,21 +951,26 @@
           <t>Cutter/Robot de cocina industrial</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>Jefe Partida</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="n">
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="n">
         <v>3000</v>
       </c>
-      <c r="H9" s="6" t="n"/>
+      <c r="H9" s="15" t="n"/>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -726,21 +986,26 @@
           <t>Balanza de precisión</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Jefe Partida</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="n">
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="n">
         <v>200</v>
       </c>
-      <c r="H10" s="6" t="n"/>
+      <c r="H10" s="15" t="n"/>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -756,21 +1021,26 @@
           <t>Mandolina profesional</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>Jefe Partida</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="n">
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="n">
         <v>150</v>
       </c>
-      <c r="H11" s="6" t="n"/>
+      <c r="H11" s="15" t="n"/>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -786,21 +1056,26 @@
           <t>Set de cortadores y aros de emplatado</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>Chef</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="n">
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="n">
         <v>300</v>
       </c>
-      <c r="H12" s="6" t="n"/>
+      <c r="H12" s="15" t="n"/>
+      <c r="I12" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -808,29 +1083,36 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Partida Carnes</t>
+          <t>Cuarto Frío</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Horno Josper HJX-25 (brasa)</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+          <t>Robot térmico tipo Thermomix</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>Chef</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="H13" s="6" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="n"/>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>La tarjeta del cap. 9 lo nombra como gancho y no aparecía en ninguno de los 141 ficheros de la familia. Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -838,29 +1120,36 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Partida Carnes</t>
+          <t>Cuarto Frío</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Plancha industrial 4 quemadores</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Sous Chef</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H14" s="6" t="n"/>
+          <t>Deshidratadora profesional de bandejas</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>Jefe Partida</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="n"/>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -868,29 +1157,36 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Partida Carnes</t>
+          <t>Cuarto Frío</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Salamandra profesional</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Sous Chef</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H15" s="6" t="n"/>
+          <t>Sifones de 1 L y cargas de N2O (set)</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Jefe Partida</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="n"/>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I15" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -898,29 +1194,36 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Partida Carnes</t>
+          <t>Cuarto Frío</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Mesa de trabajo inox 2m</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
+          <t>Termoselladora de barquetas para mise en place</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>500</v>
-      </c>
-      <c r="H16" s="6" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="n"/>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I16" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -928,29 +1231,36 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Partida Carnes</t>
+          <t>Cuarto Frío</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Sierra de huesos</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Jefe Partida</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H17" s="6" t="n"/>
+          <t>Armario de maduración y curado controlado</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Chef</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="n"/>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I17" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -963,24 +1273,29 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Termómetro de sonda digital</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Jefe Partida</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>80</v>
-      </c>
-      <c r="H18" s="6" t="n"/>
+          <t>Horno Josper HJX-25 (brasa)</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Chef</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H18" s="15" t="n"/>
+      <c r="I18" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -988,29 +1303,34 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Partida Pescados</t>
+          <t>Partida Carnes</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Plancha lisa/ranurada combinada</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
+          <t>Plancha industrial 4 quemadores</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>1800</v>
-      </c>
-      <c r="H19" s="6" t="n"/>
+      <c r="E19" s="16" t="n"/>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H19" s="15" t="n"/>
+      <c r="I19" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1018,29 +1338,34 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Partida Pescados</t>
+          <t>Partida Carnes</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Mesa de trabajo inox con balda</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
+          <t>Salamandra profesional</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>500</v>
-      </c>
-      <c r="H20" s="6" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H20" s="15" t="n"/>
+      <c r="I20" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1048,29 +1373,34 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Partida Pescados</t>
+          <t>Partida Carnes</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Sartenes de hierro fundido (set)</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Jefe Partida</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="n">
-        <v>300</v>
-      </c>
-      <c r="H21" s="6" t="n"/>
+          <t>Mesa de trabajo inox 2m</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Sous Chef</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="n">
+        <v>500</v>
+      </c>
+      <c r="H21" s="15" t="n"/>
+      <c r="I21" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1078,29 +1408,34 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Partida Pescados</t>
+          <t>Partida Carnes</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Escamador eléctrico</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
+          <t>Sierra de huesos</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>Jefe Partida</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>250</v>
-      </c>
-      <c r="H22" s="6" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H22" s="15" t="n"/>
+      <c r="I22" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1108,29 +1443,34 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Partida Pescados</t>
+          <t>Partida Carnes</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Pinzas de espinas profesionales</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+          <t>Termómetro de sonda digital</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>Jefe Partida</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="H23" s="6" t="n"/>
+      <c r="E23" s="16" t="n"/>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="H23" s="15" t="n"/>
+      <c r="I23" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1138,29 +1478,36 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Cocina Caliente</t>
+          <t>Partida Carnes</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Cocina industrial 6 fuegos + horno</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Chef</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>5200</v>
-      </c>
-      <c r="H24" s="6" t="n"/>
+          <t>Ahumador en frío / pistola de humo con virutas</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Jefe Partida</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="n"/>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I24" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1168,29 +1515,36 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Cocina Caliente</t>
+          <t>Partida Carnes</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Cocina industrial 4 fuegos auxiliar</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+          <t>Cuchillería profesional y estación de afilado (piedras y chaira)</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
         <is>
           <t>Chef</t>
         </is>
       </c>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="n">
-        <v>3500</v>
-      </c>
-      <c r="H25" s="6" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="n"/>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I25" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -1198,29 +1552,36 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Cocina Caliente</t>
+          <t>Partida Carnes</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Roner / sous-vide profesional</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Sous Chef</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H26" s="6" t="n"/>
+          <t>Rebanadora de producto congelado para tataki y carpaccios</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>Jefe Partida</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="n"/>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="n"/>
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I26" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -1228,29 +1589,34 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Cocina Caliente</t>
+          <t>Partida Pescados</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Marmita basculante 50L</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Chef</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H27" s="6" t="n"/>
+          <t>Plancha lisa/ranurada combinada</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>Sous Chef</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="n"/>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H27" s="15" t="n"/>
+      <c r="I27" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -1258,29 +1624,34 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Cocina Caliente</t>
+          <t>Partida Pescados</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Freidora doble cuba 10+10L</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
+          <t>Mesa de trabajo inox con balda</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="n">
-        <v>1800</v>
-      </c>
-      <c r="H28" s="6" t="n"/>
+      <c r="E28" s="16" t="n"/>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="n">
+        <v>500</v>
+      </c>
+      <c r="H28" s="15" t="n"/>
+      <c r="I28" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -1288,29 +1659,34 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Cocina Caliente</t>
+          <t>Partida Pescados</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Baño maría 3 cubetas GN</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Sous Chef</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="n">
-        <v>600</v>
-      </c>
-      <c r="H29" s="6" t="n"/>
+          <t>Sartenes de hierro fundido (set)</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>Jefe Partida</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="H29" s="15" t="n"/>
+      <c r="I29" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -1318,29 +1694,34 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Cocina Caliente</t>
+          <t>Partida Pescados</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Sartenes y ollas profesionales (set)</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Chef</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H30" s="6" t="n"/>
+          <t>Escamador eléctrico</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>Jefe Partida</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="n">
+        <v>250</v>
+      </c>
+      <c r="H30" s="15" t="n"/>
+      <c r="I30" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -1348,29 +1729,34 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Pastelería/Obrador</t>
+          <t>Partida Pescados</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Horno de convección 10 GN</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Chef Pastelero</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H31" s="6" t="n"/>
+          <t>Pinzas de espinas profesionales</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>Jefe Partida</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="H31" s="15" t="n"/>
+      <c r="I31" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -1378,29 +1764,36 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Pastelería/Obrador</t>
+          <t>Partida Pescados</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Amasadora planetaria 20L</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>Chef Pastelero</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>2500</v>
-      </c>
-      <c r="H32" s="6" t="n"/>
+          <t>Máquina de hielo en escamas y cuba de conservación</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>Sous Chef</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="n"/>
+      <c r="H32" s="15" t="inlineStr">
+        <is>
+          <t>Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I32" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -1408,29 +1801,36 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Pastelería/Obrador</t>
+          <t>Partida Pescados</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Heladera batch freezer</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Chef Pastelero</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H33" s="6" t="n"/>
+          <t>Expositor de pescado sobre hielo para mise en place</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>Jefe Partida</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="n"/>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="n"/>
+      <c r="H33" s="15" t="inlineStr">
+        <is>
+          <t>Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I33" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -1438,29 +1838,36 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Pastelería/Obrador</t>
+          <t>Partida Pescados</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Temperadora de chocolate</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>Chef Pastelero</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="n"/>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H34" s="6" t="n"/>
+          <t>Verificar que el abatidor alcanza ‑20 °C / ‑35 °C para la congelación preventiva de anisakis</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>Chef</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="n"/>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="n"/>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>No todos los abatidores llegan. Si el tuyo no baja de ‑20 °C, necesitas un congelador de choque: sin él no puedes servir crudos ni marinados. Va unido al bloque de anisakis del checklist APPCC.</t>
+        </is>
+      </c>
+      <c r="I34" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -1468,29 +1875,38 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Pastelería/Obrador</t>
+          <t>Cocina Caliente</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Laminadora de masas</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Chef Pastelero</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H35" s="6" t="n"/>
+          <t>Cocina industrial 6 fuegos + horno</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>Chef</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="n"/>
+      <c r="F35" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="n">
+        <v>5200</v>
+      </c>
+      <c r="H35" s="15" t="inlineStr">
+        <is>
+          <t>Escalón de gama PROFESIONAL ESTÁNDAR. El bloque modular de alta gama es la línea nueva de esta misma categoría: en un gastronómico que aspira a estrella son dos decisiones distintas, no la misma partida.</t>
+        </is>
+      </c>
+      <c r="I35" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -1498,29 +1914,34 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Pastelería/Obrador</t>
+          <t>Cocina Caliente</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Abatidor de temperatura (compartido)</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Chef Pastelero</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="n"/>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="6" t="n"/>
+          <t>Cocina industrial 4 fuegos auxiliar</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>Chef</t>
+        </is>
+      </c>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="n">
+        <v>3500</v>
+      </c>
+      <c r="H36" s="15" t="n"/>
+      <c r="I36" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -1528,29 +1949,34 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Pastelería/Obrador</t>
+          <t>Cocina Caliente</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Moldes, aros y utensilios pastelería</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Chef Pastelero</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H37" s="6" t="n"/>
+          <t>Roner / sous-vide profesional</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>Sous Chef</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="n"/>
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H37" s="15" t="n"/>
+      <c r="I37" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -1558,29 +1984,34 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Pase/Expedición</t>
+          <t>Cocina Caliente</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Mesa caliente pass-through con lámparas IR</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
+          <t>Marmita basculante 50L</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>Chef</t>
         </is>
       </c>
-      <c r="E38" s="6" t="n"/>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H38" s="6" t="n"/>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H38" s="15" t="n"/>
+      <c r="I38" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -1588,29 +2019,34 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Pase/Expedición</t>
+          <t>Cocina Caliente</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Campana extractora industrial</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Instalador</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="n"/>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="n">
-        <v>2500</v>
-      </c>
-      <c r="H39" s="6" t="n"/>
+          <t>Freidora doble cuba 10+10L</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>Sous Chef</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="n"/>
+      <c r="F39" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G39" s="17" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H39" s="15" t="n"/>
+      <c r="I39" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -1618,29 +2054,34 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Pase/Expedición</t>
+          <t>Cocina Caliente</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Lámparas de calor infrarrojo (×4)</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>Chef</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="n"/>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="n">
-        <v>800</v>
-      </c>
-      <c r="H40" s="6" t="n"/>
+          <t>Baño maría 3 cubetas GN</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>Sous Chef</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="n"/>
+      <c r="F40" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="n">
+        <v>600</v>
+      </c>
+      <c r="H40" s="15" t="n"/>
+      <c r="I40" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -1648,29 +2089,34 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Pase/Expedición</t>
+          <t>Cocina Caliente</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Timbre/campana de servicio</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
+          <t>Sartenes y ollas profesionales (set)</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
         <is>
           <t>Chef</t>
         </is>
       </c>
-      <c r="E41" s="6" t="n"/>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="H41" s="6" t="n"/>
+      <c r="E41" s="16" t="n"/>
+      <c r="F41" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H41" s="15" t="n"/>
+      <c r="I41" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -1678,29 +2124,38 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Pase/Expedición</t>
+          <t>Cocina Caliente</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Iluminación de emplatado (4000K)</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>Instalador</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="n"/>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>500</v>
-      </c>
-      <c r="H42" s="6" t="n"/>
+          <t>Horno mixto 10 GN (Rational o equivalente)</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>Chef</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="n">
+        <v>17500</v>
+      </c>
+      <c r="H42" s="15" t="inlineStr">
+        <is>
+          <t>Es el equipo nº 1 de la tabla 1 del propio libro y NO estaba en las 54 filas del checklist. La única línea de horno era el de convección de pastelería (6.000 €), que es otra cosa.</t>
+        </is>
+      </c>
+      <c r="I42" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -1708,29 +2163,36 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Almacenamiento</t>
+          <t>Cocina Caliente</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Cámara frigorífica modular conservación</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
+          <t>Bloque modular de cocción de alta gama (alternativa al bloque estándar)</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
         <is>
           <t>Chef</t>
         </is>
       </c>
-      <c r="E43" s="6" t="n"/>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="n">
-        <v>2500</v>
-      </c>
-      <c r="H43" s="6" t="n"/>
+      <c r="E43" s="16" t="n"/>
+      <c r="F43" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="n"/>
+      <c r="H43" s="15" t="inlineStr">
+        <is>
+          <t>El bloque de 6 fuegos está presupuestado a 5.200 € —precio de hostelería estándar— en una guía que enseña a aspirar a estrella. Son dos escalones distintos: elige uno y pon el otro a 0. Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I43" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -1738,29 +2200,36 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Almacenamiento</t>
+          <t>Cocina Caliente</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Cámara frigorífica modular congelación</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>Chef</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="n"/>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H44" s="6" t="n"/>
+          <t>Placa de inducción de alto rendimiento para el pase (2 zonas)</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>Sous Chef</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="n"/>
+      <c r="F44" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G44" s="17" t="n"/>
+      <c r="H44" s="15" t="inlineStr">
+        <is>
+          <t>Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I44" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -1768,29 +2237,36 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Almacenamiento</t>
+          <t>Cocina Caliente</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Armario frigorífico 600L</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
+          <t>Segundo roner y cuba termostática para servicio en paralelo</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E45" s="6" t="n"/>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H45" s="6" t="n"/>
+      <c r="E45" s="16" t="n"/>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="n"/>
+      <c r="H45" s="15" t="inlineStr">
+        <is>
+          <t>Con un solo roner no se sostienen dos binomios distintos en el mismo servicio. Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I45" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -1798,29 +2274,36 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Almacenamiento</t>
+          <t>Cocina Caliente</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Armario congelador 1400L</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>Sous Chef</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H46" s="6" t="n"/>
+          <t>Sonda multipunto con registro para cocción a baja temperatura</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>Resp. APPCC</t>
+        </is>
+      </c>
+      <c r="E46" s="16" t="n"/>
+      <c r="F46" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="n"/>
+      <c r="H46" s="15" t="inlineStr">
+        <is>
+          <t>Es el equipo que produce el «registro de sonda por lote» que pide el bloque nuevo del APPCC. Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I46" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -1828,29 +2311,36 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Almacenamiento</t>
+          <t>Cocina Caliente</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Estanterías inox almacén seco (×4)</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
+          <t>Juego completo de cubetas gastronorm y contenedores herméticos</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E47" s="6" t="n"/>
-      <c r="F47" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H47" s="6" t="n"/>
+      <c r="E47" s="16" t="n"/>
+      <c r="F47" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G47" s="17" t="n"/>
+      <c r="H47" s="15" t="inlineStr">
+        <is>
+          <t>Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I47" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -1858,29 +2348,34 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Plonge/Lavado</t>
+          <t>Pastelería/Obrador</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Lavavajillas de capota 50×50</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="n"/>
-      <c r="F48" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="n">
-        <v>3500</v>
-      </c>
-      <c r="H48" s="6" t="n"/>
+          <t>Horno de convección 10 GN</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>Chef Pastelero</t>
+        </is>
+      </c>
+      <c r="E48" s="16" t="n"/>
+      <c r="F48" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G48" s="17" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H48" s="15" t="n"/>
+      <c r="I48" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -1888,29 +2383,34 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Plonge/Lavado</t>
+          <t>Pastelería/Obrador</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Fregadero industrial doble seno</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="n"/>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="n">
-        <v>800</v>
-      </c>
-      <c r="H49" s="6" t="n"/>
+          <t>Amasadora planetaria 20L</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>Chef Pastelero</t>
+        </is>
+      </c>
+      <c r="E49" s="16" t="n"/>
+      <c r="F49" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H49" s="15" t="n"/>
+      <c r="I49" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -1918,29 +2418,34 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Plonge/Lavado</t>
+          <t>Pastelería/Obrador</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Estantería escurrido vajilla</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="n"/>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="n">
-        <v>400</v>
-      </c>
-      <c r="H50" s="6" t="n"/>
+          <t>Heladera batch freezer</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>Chef Pastelero</t>
+        </is>
+      </c>
+      <c r="E50" s="16" t="n"/>
+      <c r="F50" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H50" s="15" t="n"/>
+      <c r="I50" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -1948,29 +2453,34 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Plonge/Lavado</t>
+          <t>Pastelería/Obrador</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Contenedores reciclaje separado</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="n"/>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="H51" s="6" t="n"/>
+          <t>Temperadora de chocolate</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>Chef Pastelero</t>
+        </is>
+      </c>
+      <c r="E51" s="16" t="n"/>
+      <c r="F51" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G51" s="17" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H51" s="15" t="n"/>
+      <c r="I51" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -1978,29 +2488,34 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Pastelería/Obrador</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>TPV principal (hardware + software)</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>Gerente</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="n"/>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="n">
+          <t>Laminadora de masas</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>Chef Pastelero</t>
+        </is>
+      </c>
+      <c r="E52" s="16" t="n"/>
+      <c r="F52" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="n">
         <v>3000</v>
       </c>
-      <c r="H52" s="6" t="n"/>
+      <c r="H52" s="15" t="n"/>
+      <c r="I52" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -2008,29 +2523,34 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Pastelería/Obrador</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>TPV auxiliar sala</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Gerente</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="n"/>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H53" s="6" t="n"/>
+          <t>Abatidor de temperatura (compartido)</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
+          <t>Chef Pastelero</t>
+        </is>
+      </c>
+      <c r="E53" s="16" t="n"/>
+      <c r="F53" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G53" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="15" t="n"/>
+      <c r="I53" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -2038,29 +2558,34 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Pastelería/Obrador</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Impresora de comandas cocina (×2)</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>Gerente</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="n"/>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G54" s="7" t="n">
-        <v>600</v>
-      </c>
-      <c r="H54" s="6" t="n"/>
+          <t>Moldes, aros y utensilios pastelería</t>
+        </is>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>Chef Pastelero</t>
+        </is>
+      </c>
+      <c r="E54" s="16" t="n"/>
+      <c r="F54" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H54" s="15" t="n"/>
+      <c r="I54" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -2068,29 +2593,36 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Pastelería/Obrador</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Tablet para reservas/hostess</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>Gerente</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="n"/>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="n">
-        <v>500</v>
-      </c>
-      <c r="H55" s="6" t="n"/>
+          <t>Pacojet (helados, purés y polvos en frío)</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="inlineStr">
+        <is>
+          <t>Chef Pastelero</t>
+        </is>
+      </c>
+      <c r="E55" s="16" t="n"/>
+      <c r="F55" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="n"/>
+      <c r="H55" s="15" t="inlineStr">
+        <is>
+          <t>Como el Thermomix: la tarjeta del cap. 9 lo nombra y no existía en ningún fichero. Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I55" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -2098,29 +2630,36 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Pastelería/Obrador</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Red WiFi profesional</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>Instalador</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="n"/>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="n">
-        <v>800</v>
-      </c>
-      <c r="H56" s="6" t="n"/>
+          <t>Armario de fermentación controlada (panadería propia)</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>Chef Pastelero</t>
+        </is>
+      </c>
+      <c r="E56" s="16" t="n"/>
+      <c r="F56" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="n"/>
+      <c r="H56" s="15" t="inlineStr">
+        <is>
+          <t>El checklist Michelin pide «pan y petit fours de producción propia»: esto es lo que hace falta para cumplirlo. Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I56" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -2128,29 +2667,36 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Pastelería/Obrador</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Sistema de sonido sala</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>Interiorista</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="n"/>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H57" s="6" t="n"/>
+          <t>Pistola de pintura para chocolate con compresor</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="inlineStr">
+        <is>
+          <t>Chef Pastelero</t>
+        </is>
+      </c>
+      <c r="E57" s="16" t="n"/>
+      <c r="F57" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G57" s="17" t="n"/>
+      <c r="H57" s="15" t="inlineStr">
+        <is>
+          <t>Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I57" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -2158,48 +2704,1614 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
+          <t>Pastelería/Obrador</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Pasteurizador / madurador de mezcla de helado</t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>Chef Pastelero</t>
+        </is>
+      </c>
+      <c r="E58" s="16" t="n"/>
+      <c r="F58" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G58" s="17" t="n"/>
+      <c r="H58" s="15" t="inlineStr">
+        <is>
+          <t>Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I58" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Pase/Expedición</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Mesa caliente pass-through con lámparas IR</t>
+        </is>
+      </c>
+      <c r="D59" s="15" t="inlineStr">
+        <is>
+          <t>Chef</t>
+        </is>
+      </c>
+      <c r="E59" s="16" t="n"/>
+      <c r="F59" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G59" s="17" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H59" s="15" t="n"/>
+      <c r="I59" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Pase/Expedición</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Campana extractora industrial</t>
+        </is>
+      </c>
+      <c r="D60" s="15" t="inlineStr">
+        <is>
+          <t>Instalador</t>
+        </is>
+      </c>
+      <c r="E60" s="16" t="n"/>
+      <c r="F60" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G60" s="17" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H60" s="15" t="inlineStr">
+        <is>
+          <t>Esto es SOLO la campana. El sistema completo hasta cubierta —conducto, ventilador, silenciador y aportación de aire— va en las líneas nuevas del bloque «Extracción e instalaciones»: el cap. 5 lo llama «obstáculo técnico número 1» y estaba presupuestado en 2.500 € en total.</t>
+        </is>
+      </c>
+      <c r="I60" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Pase/Expedición</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Lámparas de calor infrarrojo (×4)</t>
+        </is>
+      </c>
+      <c r="D61" s="15" t="inlineStr">
+        <is>
+          <t>Chef</t>
+        </is>
+      </c>
+      <c r="E61" s="16" t="n"/>
+      <c r="F61" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G61" s="17" t="n">
+        <v>800</v>
+      </c>
+      <c r="H61" s="15" t="n"/>
+      <c r="I61" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Pase/Expedición</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Timbre/campana de servicio</t>
+        </is>
+      </c>
+      <c r="D62" s="15" t="inlineStr">
+        <is>
+          <t>Chef</t>
+        </is>
+      </c>
+      <c r="E62" s="16" t="n"/>
+      <c r="F62" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G62" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="H62" s="15" t="n"/>
+      <c r="I62" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Pase/Expedición</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Iluminación de emplatado (4000K)</t>
+        </is>
+      </c>
+      <c r="D63" s="15" t="inlineStr">
+        <is>
+          <t>Instalador</t>
+        </is>
+      </c>
+      <c r="E63" s="16" t="n"/>
+      <c r="F63" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G63" s="17" t="n">
+        <v>500</v>
+      </c>
+      <c r="H63" s="15" t="n"/>
+      <c r="I63" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Pase/Expedición</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Carro caliente de mantenimiento para eventos y comedor privado</t>
+        </is>
+      </c>
+      <c r="D64" s="15" t="inlineStr">
+        <is>
+          <t>Chef</t>
+        </is>
+      </c>
+      <c r="E64" s="16" t="n"/>
+      <c r="F64" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G64" s="17" t="n"/>
+      <c r="H64" s="15" t="inlineStr">
+        <is>
+          <t>El checklist de sala presupuesta un comedor privado / chef's table de 8‑10 plazas: hay que llegar hasta allí con el plato caliente. Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I64" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Pase/Expedición</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Temporizadores de pase y reloj de cocina (set)</t>
+        </is>
+      </c>
+      <c r="D65" s="15" t="inlineStr">
+        <is>
+          <t>Chef</t>
+        </is>
+      </c>
+      <c r="E65" s="16" t="n"/>
+      <c r="F65" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G65" s="17" t="n"/>
+      <c r="H65" s="15" t="inlineStr">
+        <is>
+          <t>El checklist Michelin exige «tiempos entre pases controlados y fluidos». Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I65" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Pase/Expedición</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Mesa de apoyo refrigerada para el pase de fríos</t>
+        </is>
+      </c>
+      <c r="D66" s="15" t="inlineStr">
+        <is>
+          <t>Chef</t>
+        </is>
+      </c>
+      <c r="E66" s="16" t="n"/>
+      <c r="F66" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="n"/>
+      <c r="H66" s="15" t="inlineStr">
+        <is>
+          <t>Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I66" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Almacenamiento</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Cámara frigorífica modular conservación</t>
+        </is>
+      </c>
+      <c r="D67" s="15" t="inlineStr">
+        <is>
+          <t>Chef</t>
+        </is>
+      </c>
+      <c r="E67" s="16" t="n"/>
+      <c r="F67" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G67" s="17" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H67" s="15" t="n"/>
+      <c r="I67" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Almacenamiento</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Cámara frigorífica modular congelación</t>
+        </is>
+      </c>
+      <c r="D68" s="15" t="inlineStr">
+        <is>
+          <t>Chef</t>
+        </is>
+      </c>
+      <c r="E68" s="16" t="n"/>
+      <c r="F68" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G68" s="17" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H68" s="15" t="n"/>
+      <c r="I68" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Almacenamiento</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Armario frigorífico 600L</t>
+        </is>
+      </c>
+      <c r="D69" s="15" t="inlineStr">
+        <is>
+          <t>Sous Chef</t>
+        </is>
+      </c>
+      <c r="E69" s="16" t="n"/>
+      <c r="F69" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G69" s="17" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H69" s="15" t="n"/>
+      <c r="I69" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Almacenamiento</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Armario congelador 1400L</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>Sous Chef</t>
+        </is>
+      </c>
+      <c r="E70" s="16" t="n"/>
+      <c r="F70" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G70" s="17" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H70" s="15" t="n"/>
+      <c r="I70" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Almacenamiento</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Estanterías inox almacén seco (×4)</t>
+        </is>
+      </c>
+      <c r="D71" s="15" t="inlineStr">
+        <is>
+          <t>Sous Chef</t>
+        </is>
+      </c>
+      <c r="E71" s="16" t="n"/>
+      <c r="F71" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G71" s="17" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H71" s="15" t="n"/>
+      <c r="I71" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Almacenamiento</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Estanterías desmontables de polipropileno para cámaras</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>Sous Chef</t>
+        </is>
+      </c>
+      <c r="E72" s="16" t="n"/>
+      <c r="F72" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G72" s="17" t="n"/>
+      <c r="H72" s="15" t="inlineStr">
+        <is>
+          <t>Desmontables porque el plan de limpieza del APPCC exige limpiar la cámara por dentro. Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I72" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Almacenamiento</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Impresora de etiquetas de trazabilidad y consumibles</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="inlineStr">
+        <is>
+          <t>Resp. APPCC</t>
+        </is>
+      </c>
+      <c r="E73" s="16" t="n"/>
+      <c r="F73" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G73" s="17" t="n"/>
+      <c r="H73" s="15" t="inlineStr">
+        <is>
+          <t>Es lo que hace posible el «etiquetado de productos con fecha y lote» del APPCC. Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I73" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Almacenamiento</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Báscula de recepción de mercancía (hasta 60 kg)</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>Resp. compras</t>
+        </is>
+      </c>
+      <c r="E74" s="16" t="n"/>
+      <c r="F74" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G74" s="17" t="n"/>
+      <c r="H74" s="15" t="inlineStr">
+        <is>
+          <t>Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I74" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Plonge/Lavado</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Lavavajillas de capota 50×50</t>
+        </is>
+      </c>
+      <c r="D75" s="15" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E75" s="16" t="n"/>
+      <c r="F75" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G75" s="17" t="n">
+        <v>3500</v>
+      </c>
+      <c r="H75" s="15" t="inlineStr">
+        <is>
+          <t>Elige UNA de las dos: capota o túnel de lavado (línea nueva del bloque Plonge/Lavado). Con menú degustación y maridaje —300‑600 copas por servicio— la capota no da abasto. Si eliges el túnel, pon esta línea a 0.</t>
+        </is>
+      </c>
+      <c r="I75" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Plonge/Lavado</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Fregadero industrial doble seno</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E76" s="16" t="n"/>
+      <c r="F76" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G76" s="17" t="n">
+        <v>800</v>
+      </c>
+      <c r="H76" s="15" t="n"/>
+      <c r="I76" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Plonge/Lavado</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Estantería escurrido vajilla</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E77" s="16" t="n"/>
+      <c r="F77" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G77" s="17" t="n">
+        <v>400</v>
+      </c>
+      <c r="H77" s="15" t="n"/>
+      <c r="I77" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Plonge/Lavado</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Contenedores reciclaje separado</t>
+        </is>
+      </c>
+      <c r="D78" s="15" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E78" s="16" t="n"/>
+      <c r="F78" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G78" s="17" t="n">
+        <v>200</v>
+      </c>
+      <c r="H78" s="15" t="n"/>
+      <c r="I78" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Plonge/Lavado</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Túnel de lavado con mesas de entrada y salida (ALTERNATIVA a la capota)</t>
+        </is>
+      </c>
+      <c r="D79" s="15" t="inlineStr">
+        <is>
+          <t>Instalador</t>
+        </is>
+      </c>
+      <c r="E79" s="16" t="n"/>
+      <c r="F79" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G79" s="17" t="n"/>
+      <c r="H79" s="15" t="inlineStr">
+        <is>
+          <t>Rango medido 12.000‑25.000 €. Va SIN importe a propósito: es una alternativa al lavavajillas de capota, no una partida adicional. Elige una de las dos y pon la otra a 0, o el presupuesto contará dos veces el mismo lavado.</t>
+        </is>
+      </c>
+      <c r="I79" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Plonge/Lavado</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Lavavasos independiente para la cristalería de maridaje</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E80" s="16" t="n"/>
+      <c r="F80" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G80" s="17" t="n"/>
+      <c r="H80" s="15" t="inlineStr">
+        <is>
+          <t>Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I80" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Plonge/Lavado</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Descalcificador y tratamiento de agua para el lavado</t>
+        </is>
+      </c>
+      <c r="D81" s="15" t="inlineStr">
+        <is>
+          <t>Instalador</t>
+        </is>
+      </c>
+      <c r="E81" s="16" t="n"/>
+      <c r="F81" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G81" s="17" t="n"/>
+      <c r="H81" s="15" t="inlineStr">
+        <is>
+          <t>Sin él, la cristalería de maridaje sale velada. Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I81" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
           <t>Tecnología</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>TPV principal (hardware + software)</t>
+        </is>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>Gerente</t>
+        </is>
+      </c>
+      <c r="E82" s="16" t="n"/>
+      <c r="F82" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G82" s="17" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H82" s="15" t="n"/>
+      <c r="I82" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>TPV auxiliar sala</t>
+        </is>
+      </c>
+      <c r="D83" s="15" t="inlineStr">
+        <is>
+          <t>Gerente</t>
+        </is>
+      </c>
+      <c r="E83" s="16" t="n"/>
+      <c r="F83" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G83" s="17" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H83" s="15" t="n"/>
+      <c r="I83" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Impresora de comandas cocina (×2)</t>
+        </is>
+      </c>
+      <c r="D84" s="15" t="inlineStr">
+        <is>
+          <t>Gerente</t>
+        </is>
+      </c>
+      <c r="E84" s="16" t="n"/>
+      <c r="F84" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G84" s="17" t="n">
+        <v>600</v>
+      </c>
+      <c r="H84" s="15" t="n"/>
+      <c r="I84" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Tablet para reservas/hostess</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="inlineStr">
+        <is>
+          <t>Gerente</t>
+        </is>
+      </c>
+      <c r="E85" s="16" t="n"/>
+      <c r="F85" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G85" s="17" t="n">
+        <v>500</v>
+      </c>
+      <c r="H85" s="15" t="n"/>
+      <c r="I85" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Red WiFi profesional</t>
+        </is>
+      </c>
+      <c r="D86" s="15" t="inlineStr">
+        <is>
+          <t>Instalador</t>
+        </is>
+      </c>
+      <c r="E86" s="16" t="n"/>
+      <c r="F86" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G86" s="17" t="n">
+        <v>800</v>
+      </c>
+      <c r="H86" s="15" t="n"/>
+      <c r="I86" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Sistema de sonido sala</t>
+        </is>
+      </c>
+      <c r="D87" s="15" t="inlineStr">
+        <is>
+          <t>Interiorista</t>
+        </is>
+      </c>
+      <c r="E87" s="16" t="n"/>
+      <c r="F87" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G87" s="17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H87" s="15" t="n"/>
+      <c r="I87" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
         <is>
           <t>Cámaras de seguridad (CCTV)</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D88" s="15" t="inlineStr">
         <is>
           <t>Instalador</t>
         </is>
       </c>
-      <c r="E58" s="6" t="n"/>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="n">
+      <c r="E88" s="16" t="n"/>
+      <c r="F88" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G88" s="17" t="n">
         <v>1500</v>
       </c>
-      <c r="H58" s="6" t="n"/>
-    </row>
-    <row r="59"/>
-    <row r="60">
-      <c r="A60" s="8" t="inlineStr">
+      <c r="H88" s="15" t="n"/>
+      <c r="I88" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>KDS: pantallas de comandas en cocina</t>
+        </is>
+      </c>
+      <c r="D89" s="15" t="inlineStr">
+        <is>
+          <t>Gerente</t>
+        </is>
+      </c>
+      <c r="E89" s="16" t="n"/>
+      <c r="F89" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G89" s="17" t="n"/>
+      <c r="H89" s="15" t="inlineStr">
+        <is>
+          <t>Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I89" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>SAI/UPS para TPV, cámaras y comunicaciones</t>
+        </is>
+      </c>
+      <c r="D90" s="15" t="inlineStr">
+        <is>
+          <t>Instalador</t>
+        </is>
+      </c>
+      <c r="E90" s="16" t="n"/>
+      <c r="F90" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G90" s="17" t="n"/>
+      <c r="H90" s="15" t="inlineStr">
+        <is>
+          <t>Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I90" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Software de escandallos y APPCC digital</t>
+        </is>
+      </c>
+      <c r="D91" s="15" t="inlineStr">
+        <is>
+          <t>Gerente</t>
+        </is>
+      </c>
+      <c r="E91" s="16" t="n"/>
+      <c r="F91" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G91" s="17" t="n"/>
+      <c r="H91" s="15" t="inlineStr">
+        <is>
+          <t>Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
+      <c r="I91" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Extracción e instalaciones</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Conducto de extracción hasta cubierta + ventilador + silenciador</t>
+        </is>
+      </c>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t>Instalador</t>
+        </is>
+      </c>
+      <c r="E92" s="16" t="n"/>
+      <c r="F92" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G92" s="17" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H92" s="15" t="inlineStr">
+        <is>
+          <t>Rango 12.000‑30.000 € según recorrido y altura; va precargado el MÍNIMO. El cap. 5 lo llama «obstáculo técnico número 1» y toda la extracción estaba presupuestada en 2.500 €.</t>
+        </is>
+      </c>
+      <c r="I92" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Extracción e instalaciones</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Sistema de aportación de aire (compensación)</t>
+        </is>
+      </c>
+      <c r="D93" s="15" t="inlineStr">
+        <is>
+          <t>Instalador</t>
+        </is>
+      </c>
+      <c r="E93" s="16" t="n"/>
+      <c r="F93" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G93" s="17" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H93" s="15" t="inlineStr">
+        <is>
+          <t>Rango 3.000‑6.000 €; precargado el mínimo. Sin aportación de aire la campana no extrae y la sala se queda en depresión.</t>
+        </is>
+      </c>
+      <c r="I93" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Extracción e instalaciones</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Sistema automático de extinción en campana (CTE DB‑SI y aseguradora)</t>
+        </is>
+      </c>
+      <c r="D94" s="15" t="inlineStr">
+        <is>
+          <t>Instalador</t>
+        </is>
+      </c>
+      <c r="E94" s="16" t="n"/>
+      <c r="F94" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G94" s="17" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H94" s="15" t="inlineStr">
+        <is>
+          <t>Rango 2.500‑4.000 €; precargado el mínimo. Con freidora es exigible, y la aseguradora lo pide para emitir la póliza. La cadena «extinción» no aparecía en ningún fichero de la familia.</t>
+        </is>
+      </c>
+      <c r="I94" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Extracción e instalaciones</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Instalación, transporte y puesta en marcha (% sobre el equipamiento)</t>
+        </is>
+      </c>
+      <c r="D95" s="15" t="inlineStr">
+        <is>
+          <t>Instalador</t>
+        </is>
+      </c>
+      <c r="E95" s="16" t="n"/>
+      <c r="F95" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G95" s="19">
+        <f>IFERROR(ROUND((SUMIFS($G$5:$G$94,$B$5:$B$94,"&lt;&gt;Extracción e instalaciones",$B$5:$B$94,"&lt;&gt;Tecnología"))*Instrucciones!$B$11,2),"")</f>
+        <v>14360.4</v>
+      </c>
+      <c r="H95" s="15" t="inlineStr">
+        <is>
+          <t>CALCULADO: es el porcentaje de la hoja «Instrucciones» aplicado a la suma del resto de partidas de este checklist. No hace falta que lo escribas: cambia solo cuando cambias el equipamiento.</t>
+        </is>
+      </c>
+      <c r="I95" s="18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="E96" s="20" t="n"/>
+      <c r="G96" s="21" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="22" t="inlineStr">
+        <is>
+          <t>RESUMEN — lo calcula el libro (v2.0)</t>
+        </is>
+      </c>
+      <c r="B97" s="23" t="n"/>
+      <c r="C97" s="23" t="n"/>
+      <c r="D97" s="23" t="n"/>
+      <c r="E97" s="23" t="n"/>
+      <c r="F97" s="23" t="n"/>
+      <c r="G97" s="23" t="n"/>
+      <c r="H97" s="23" t="n"/>
+      <c r="I97" s="23" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL PRESUPUESTADO (€)</t>
+        </is>
+      </c>
+      <c r="G98" s="24">
+        <f>SUMIF($I$5:$I$95,"Sí",$G$5:$G$95)</f>
+        <v>161430.4</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>Partidas SIN importe (a presupuestar)</t>
+        </is>
+      </c>
+      <c r="G99" s="25">
+        <f>COUNTIF(B5:B95,"&lt;&gt;")-COUNT(G5:G95)</f>
+        <v>32.0</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>El TOTAL de arriba es un SUELO: no incluye estas partidas, que van a presupuestar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t>Avance del checklist (% completado)</t>
+        </is>
+      </c>
+      <c r="F100" s="26">
+        <f>IFERROR(COUNTIF(F5:F95,"Completado")/COUNTIF(F5:F95,"&lt;&gt;"),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Estado terminal de este checklist: «Completado»</t>
+        </is>
+      </c>
+    </row>
+    <row r="101"/>
+    <row r="102">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>SUBTOTALES POR CATEGORÍA</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Cuarto Frío</t>
+        </is>
+      </c>
+      <c r="G103" s="21">
+        <f>SUMIFS($G$5:$G$95,$B$5:$B$95,$A103,$I$5:$I$95,"Sí")</f>
+        <v>15850.0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Partida Carnes</t>
+        </is>
+      </c>
+      <c r="G104" s="21">
+        <f>SUMIFS($G$5:$G$95,$B$5:$B$95,$A104,$I$5:$I$95,"Sí")</f>
+        <v>18080.0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Partida Pescados</t>
+        </is>
+      </c>
+      <c r="G105" s="21">
+        <f>SUMIFS($G$5:$G$95,$B$5:$B$95,$A105,$I$5:$I$95,"Sí")</f>
+        <v>2890.0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Cocina Caliente</t>
+        </is>
+      </c>
+      <c r="G106" s="21">
+        <f>SUMIFS($G$5:$G$95,$B$5:$B$95,$A106,$I$5:$I$95,"Sí")</f>
+        <v>36100.0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Pastelería/Obrador</t>
+        </is>
+      </c>
+      <c r="G107" s="21">
+        <f>SUMIFS($G$5:$G$95,$B$5:$B$95,$A107,$I$5:$I$95,"Sí")</f>
+        <v>19000.0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Pase/Expedición</t>
+        </is>
+      </c>
+      <c r="G108" s="21">
+        <f>SUMIFS($G$5:$G$95,$B$5:$B$95,$A108,$I$5:$I$95,"Sí")</f>
+        <v>6850.0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Almacenamiento</t>
+        </is>
+      </c>
+      <c r="G109" s="21">
+        <f>SUMIFS($G$5:$G$95,$B$5:$B$95,$A109,$I$5:$I$95,"Sí")</f>
+        <v>16000.0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Plonge/Lavado</t>
+        </is>
+      </c>
+      <c r="G110" s="21">
+        <f>SUMIFS($G$5:$G$95,$B$5:$B$95,$A110,$I$5:$I$95,"Sí")</f>
+        <v>4900.0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="G111" s="21">
+        <f>SUMIFS($G$5:$G$95,$B$5:$B$95,$A111,$I$5:$I$95,"Sí")</f>
+        <v>9900.0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Extracción e instalaciones</t>
+        </is>
+      </c>
+      <c r="G112" s="21">
+        <f>SUMIFS($G$5:$G$95,$B$5:$B$95,$A112,$I$5:$I$95,"Sí")</f>
+        <v>31860.4</v>
+      </c>
+    </row>
+    <row r="113"/>
+    <row r="114">
+      <c r="A114" t="inlineStr">
         <is>
           <t>AI Chef Pro · aichef.pro — Restaurante Gastronómico</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <autoFilter ref="A4:H4"/>
   <mergeCells count="3">
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A114:I114"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A60:H60"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <conditionalFormatting sqref="I5:I95">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
+      <formula>"Sí"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1" stopIfTrue="1">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:F95">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0" stopIfTrue="1">
+      <formula>"Completado"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="1" stopIfTrue="1">
+      <formula>"En Curso"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="2" stopIfTrue="1">
+      <formula>"Pendiente"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G99">
+    <cfRule type="expression" priority="6" dxfId="1" stopIfTrue="1">
+      <formula>=AND(ISNUMBER(G99),G99&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation sqref="I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I64 I65 I66 I67 I68 I69 I70 I71 I72 I73 I74 I75 I76 I77 I78 I79 I80 I81 I82 I83 I84 I85 I86 I87 I88 I89 I90 I91 I92 I93 I94 I95" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Incluir en el total" error="Escribe «Sí» o «No». Las líneas marcadas «No» no suman en el TOTAL ni en los subtotales: son la opción que NO has elegido." type="list">
+      <formula1>"Sí,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53 E54 E55 E56 E57 E58 E59 E60 E61 E62 E63 E64 E65 E66 E67 E68 E69 E70 E71 E72 E73 E74 E75 E76 E77 E78 E79 E80 E81 E82 E83 E84 E85 E86 E87 E88 E89 E90 E91 E92 E93 E94 E95" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fecha no válida" error="Escribe una fecha (dd/mm/aaaa) entre 2020 y 2040." type="date" operator="between">
+      <formula1>DATE(2020,1,1)</formula1>
+      <formula2>DATE(2040,12,31)</formula2>
+    </dataValidation>
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista: Pendiente, En Curso, Completado" type="list">
       <formula1>"Pendiente,En Curso,Completado"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 G70 G71 G72 G73 G74 G75 G76 G77 G78 G79 G80 G81 G82 G83 G84 G85 G86 G87 G88 G89 G90 G91 G92 G93 G94" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Importe no válido" error="Escribe un número mayor o igual que 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/guia-restaurante-gastronomico/checklist-equipamiento-cocina.xlsx
+++ b/astro-site/public/dl/guia-restaurante-gastronomico/checklist-equipamiento-cocina.xlsx
@@ -130,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -190,6 +190,10 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4099,169 +4103,286 @@
       <c r="I97" s="23" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="11" t="inlineStr">
+      <c r="A98" s="22" t="inlineStr">
         <is>
           <t>TOTAL PRESUPUESTADO (€)</t>
         </is>
       </c>
-      <c r="G98" s="24">
+      <c r="B98" s="23" t="n"/>
+      <c r="C98" s="23" t="n"/>
+      <c r="D98" s="23" t="n"/>
+      <c r="E98" s="23" t="n"/>
+      <c r="F98" s="23" t="n"/>
+      <c r="G98" s="27">
         <f>SUMIF($I$5:$I$95,"Sí",$G$5:$G$95)</f>
         <v>161430.4</v>
       </c>
+      <c r="H98" s="23" t="n"/>
+      <c r="I98" s="23" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="11" t="inlineStr">
+      <c r="A99" s="22" t="inlineStr">
         <is>
           <t>Partidas SIN importe (a presupuestar)</t>
         </is>
       </c>
-      <c r="G99" s="25">
+      <c r="B99" s="23" t="n"/>
+      <c r="C99" s="23" t="n"/>
+      <c r="D99" s="23" t="n"/>
+      <c r="E99" s="23" t="n"/>
+      <c r="F99" s="23" t="n"/>
+      <c r="G99" s="28">
         <f>COUNTIF(B5:B95,"&lt;&gt;")-COUNT(G5:G95)</f>
         <v>32.0</v>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H99" s="23" t="inlineStr">
         <is>
           <t>El TOTAL de arriba es un SUELO: no incluye estas partidas, que van a presupuestar.</t>
         </is>
       </c>
+      <c r="I99" s="23" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="11" t="inlineStr">
+      <c r="A100" s="22" t="inlineStr">
         <is>
           <t>Avance del checklist (% completado)</t>
         </is>
       </c>
-      <c r="F100" s="26">
+      <c r="B100" s="23" t="n"/>
+      <c r="C100" s="23" t="n"/>
+      <c r="D100" s="23" t="n"/>
+      <c r="E100" s="23" t="n"/>
+      <c r="F100" s="29">
         <f>IFERROR(COUNTIF(F5:F95,"Completado")/COUNTIF(F5:F95,"&lt;&gt;"),"")</f>
         <v>0.0</v>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G100" s="23" t="inlineStr">
         <is>
           <t>Estado terminal de este checklist: «Completado»</t>
         </is>
       </c>
-    </row>
-    <row r="101"/>
+      <c r="H100" s="23" t="n"/>
+      <c r="I100" s="23" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="23" t="n"/>
+      <c r="B101" s="23" t="n"/>
+      <c r="C101" s="23" t="n"/>
+      <c r="D101" s="23" t="n"/>
+      <c r="E101" s="23" t="n"/>
+      <c r="F101" s="23" t="n"/>
+      <c r="G101" s="23" t="n"/>
+      <c r="H101" s="23" t="n"/>
+      <c r="I101" s="23" t="n"/>
+    </row>
     <row r="102">
-      <c r="A102" s="11" t="inlineStr">
+      <c r="A102" s="22" t="inlineStr">
         <is>
           <t>SUBTOTALES POR CATEGORÍA</t>
         </is>
       </c>
+      <c r="B102" s="23" t="n"/>
+      <c r="C102" s="23" t="n"/>
+      <c r="D102" s="23" t="n"/>
+      <c r="E102" s="23" t="n"/>
+      <c r="F102" s="23" t="n"/>
+      <c r="G102" s="23" t="n"/>
+      <c r="H102" s="23" t="n"/>
+      <c r="I102" s="23" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="23" t="inlineStr">
         <is>
           <t>Cuarto Frío</t>
         </is>
       </c>
-      <c r="G103" s="21">
+      <c r="B103" s="23" t="n"/>
+      <c r="C103" s="23" t="n"/>
+      <c r="D103" s="23" t="n"/>
+      <c r="E103" s="23" t="n"/>
+      <c r="F103" s="23" t="n"/>
+      <c r="G103" s="30">
         <f>SUMIFS($G$5:$G$95,$B$5:$B$95,$A103,$I$5:$I$95,"Sí")</f>
         <v>15850.0</v>
       </c>
+      <c r="H103" s="23" t="n"/>
+      <c r="I103" s="23" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="23" t="inlineStr">
         <is>
           <t>Partida Carnes</t>
         </is>
       </c>
-      <c r="G104" s="21">
+      <c r="B104" s="23" t="n"/>
+      <c r="C104" s="23" t="n"/>
+      <c r="D104" s="23" t="n"/>
+      <c r="E104" s="23" t="n"/>
+      <c r="F104" s="23" t="n"/>
+      <c r="G104" s="30">
         <f>SUMIFS($G$5:$G$95,$B$5:$B$95,$A104,$I$5:$I$95,"Sí")</f>
         <v>18080.0</v>
       </c>
+      <c r="H104" s="23" t="n"/>
+      <c r="I104" s="23" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="23" t="inlineStr">
         <is>
           <t>Partida Pescados</t>
         </is>
       </c>
-      <c r="G105" s="21">
+      <c r="B105" s="23" t="n"/>
+      <c r="C105" s="23" t="n"/>
+      <c r="D105" s="23" t="n"/>
+      <c r="E105" s="23" t="n"/>
+      <c r="F105" s="23" t="n"/>
+      <c r="G105" s="30">
         <f>SUMIFS($G$5:$G$95,$B$5:$B$95,$A105,$I$5:$I$95,"Sí")</f>
         <v>2890.0</v>
       </c>
+      <c r="H105" s="23" t="n"/>
+      <c r="I105" s="23" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="23" t="inlineStr">
         <is>
           <t>Cocina Caliente</t>
         </is>
       </c>
-      <c r="G106" s="21">
+      <c r="B106" s="23" t="n"/>
+      <c r="C106" s="23" t="n"/>
+      <c r="D106" s="23" t="n"/>
+      <c r="E106" s="23" t="n"/>
+      <c r="F106" s="23" t="n"/>
+      <c r="G106" s="30">
         <f>SUMIFS($G$5:$G$95,$B$5:$B$95,$A106,$I$5:$I$95,"Sí")</f>
         <v>36100.0</v>
       </c>
+      <c r="H106" s="23" t="n"/>
+      <c r="I106" s="23" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="23" t="inlineStr">
         <is>
           <t>Pastelería/Obrador</t>
         </is>
       </c>
-      <c r="G107" s="21">
+      <c r="B107" s="23" t="n"/>
+      <c r="C107" s="23" t="n"/>
+      <c r="D107" s="23" t="n"/>
+      <c r="E107" s="23" t="n"/>
+      <c r="F107" s="23" t="n"/>
+      <c r="G107" s="30">
         <f>SUMIFS($G$5:$G$95,$B$5:$B$95,$A107,$I$5:$I$95,"Sí")</f>
         <v>19000.0</v>
       </c>
+      <c r="H107" s="23" t="n"/>
+      <c r="I107" s="23" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="23" t="inlineStr">
         <is>
           <t>Pase/Expedición</t>
         </is>
       </c>
-      <c r="G108" s="21">
+      <c r="B108" s="23" t="n"/>
+      <c r="C108" s="23" t="n"/>
+      <c r="D108" s="23" t="n"/>
+      <c r="E108" s="23" t="n"/>
+      <c r="F108" s="23" t="n"/>
+      <c r="G108" s="30">
         <f>SUMIFS($G$5:$G$95,$B$5:$B$95,$A108,$I$5:$I$95,"Sí")</f>
         <v>6850.0</v>
       </c>
+      <c r="H108" s="23" t="n"/>
+      <c r="I108" s="23" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="23" t="inlineStr">
         <is>
           <t>Almacenamiento</t>
         </is>
       </c>
-      <c r="G109" s="21">
+      <c r="B109" s="23" t="n"/>
+      <c r="C109" s="23" t="n"/>
+      <c r="D109" s="23" t="n"/>
+      <c r="E109" s="23" t="n"/>
+      <c r="F109" s="23" t="n"/>
+      <c r="G109" s="30">
         <f>SUMIFS($G$5:$G$95,$B$5:$B$95,$A109,$I$5:$I$95,"Sí")</f>
         <v>16000.0</v>
       </c>
+      <c r="H109" s="23" t="n"/>
+      <c r="I109" s="23" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="23" t="inlineStr">
         <is>
           <t>Plonge/Lavado</t>
         </is>
       </c>
-      <c r="G110" s="21">
+      <c r="B110" s="23" t="n"/>
+      <c r="C110" s="23" t="n"/>
+      <c r="D110" s="23" t="n"/>
+      <c r="E110" s="23" t="n"/>
+      <c r="F110" s="23" t="n"/>
+      <c r="G110" s="30">
         <f>SUMIFS($G$5:$G$95,$B$5:$B$95,$A110,$I$5:$I$95,"Sí")</f>
         <v>4900.0</v>
       </c>
+      <c r="H110" s="23" t="n"/>
+      <c r="I110" s="23" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="23" t="inlineStr">
         <is>
           <t>Tecnología</t>
         </is>
       </c>
-      <c r="G111" s="21">
+      <c r="B111" s="23" t="n"/>
+      <c r="C111" s="23" t="n"/>
+      <c r="D111" s="23" t="n"/>
+      <c r="E111" s="23" t="n"/>
+      <c r="F111" s="23" t="n"/>
+      <c r="G111" s="30">
         <f>SUMIFS($G$5:$G$95,$B$5:$B$95,$A111,$I$5:$I$95,"Sí")</f>
         <v>9900.0</v>
       </c>
+      <c r="H111" s="23" t="n"/>
+      <c r="I111" s="23" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="23" t="inlineStr">
         <is>
           <t>Extracción e instalaciones</t>
         </is>
       </c>
-      <c r="G112" s="21">
+      <c r="B112" s="23" t="n"/>
+      <c r="C112" s="23" t="n"/>
+      <c r="D112" s="23" t="n"/>
+      <c r="E112" s="23" t="n"/>
+      <c r="F112" s="23" t="n"/>
+      <c r="G112" s="30">
         <f>SUMIFS($G$5:$G$95,$B$5:$B$95,$A112,$I$5:$I$95,"Sí")</f>
         <v>31860.4</v>
       </c>
-    </row>
-    <row r="113"/>
+      <c r="H112" s="23" t="n"/>
+      <c r="I112" s="23" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="23" t="n"/>
+      <c r="B113" s="23" t="n"/>
+      <c r="C113" s="23" t="n"/>
+      <c r="D113" s="23" t="n"/>
+      <c r="E113" s="23" t="n"/>
+      <c r="F113" s="23" t="n"/>
+      <c r="G113" s="23" t="n"/>
+      <c r="H113" s="23" t="n"/>
+      <c r="I113" s="23" t="n"/>
+    </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="23" t="inlineStr">
         <is>
           <t>AI Chef Pro · aichef.pro — Restaurante Gastronómico</t>
         </is>
@@ -4276,21 +4397,21 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="I5:I95">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="0" stopIfTrue="1">
       <formula>"Sí"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F95">
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0" stopIfTrue="1">
       <formula>"Completado"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"En Curso"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="2" stopIfTrue="1">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="2" stopIfTrue="1">
       <formula>"Pendiente"</formula>
     </cfRule>
   </conditionalFormatting>
